--- a/data/trans_dic/IP25A_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Habitat-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,16; 18,15</t>
+          <t>7,4; 19,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 18,79</t>
+          <t>8,61; 17,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 16,82</t>
+          <t>8,97; 16,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 16,88</t>
+          <t>9,32; 17,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 18,16</t>
+          <t>7,95; 16,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 15,73</t>
+          <t>9,8; 15,79</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 25,66</t>
+          <t>10,89; 20,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 20,46</t>
+          <t>14,48; 25,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 21,34</t>
+          <t>13,85; 21,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 15,22</t>
+          <t>9,88; 19,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 19,07</t>
+          <t>7,29; 15,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,77</t>
+          <t>9,92; 15,82</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,42</t>
+          <t>11,64; 16,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,22</t>
+          <t>11,52; 16,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,79</t>
+          <t>12,11; 15,52</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>30226</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9297; 20687</t>
+          <t>9320; 24319</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10443; 26378</t>
+          <t>10156; 21057</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23381; 42781</t>
+          <t>21877; 40256</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>30633</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>51766</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15983; 31859</t>
+          <t>21886; 41974</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23426; 45840</t>
+          <t>14536; 29237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43553; 69398</t>
+          <t>40910; 65923</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>26157</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>29852</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62861</t>
+          <t>56009</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19726; 47727</t>
+          <t>18331; 34814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20006; 37914</t>
+          <t>22074; 39101</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45900; 79212</t>
+          <t>44443; 69256</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42922</t>
+          <t>41946</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11955; 25191</t>
+          <t>16690; 32370</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17810; 34457</t>
+          <t>12010; 25677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32987; 54592</t>
+          <t>33116; 52794</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>96010</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72364; 107420</t>
+          <t>81248; 112983</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87401; 123075</t>
+          <t>71183; 99093</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171524; 223073</t>
+          <t>159367; 204211</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,4; 19,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8,61; 17,85</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,97; 16,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,32; 17,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,95; 16,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,8; 15,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,89; 20,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>14,48; 25,64</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13,85; 21,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9,88; 19,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,29; 15,58</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,92; 15,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>11,64; 16,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11,52; 16,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12,11; 15,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1233051543796451</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1246022386547134</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1239326221469668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>15525</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14701</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30226</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.07402387177437615</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.08608378567758551</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.0896995177387095</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9320; 24319</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10156; 21057</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21877; 40256</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1931507329140923</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1784763683224733</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1650609973335489</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1304907215615597</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1156209748095396</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1239813417954284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>30633</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21133</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51766</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.09323172424366191</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.07952731345608309</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.0979807763995988</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>21886; 41974</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>14536; 29237</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>40910; 65923</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1788005790119912</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1599593882445466</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1578880006679359</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1553788573214627</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1957619655587151</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1745729069549455</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>29852</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56009</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1088916980744003</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1447559342470074</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1385255288279815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>18331; 34814</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>22074; 39101</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>44443; 69256</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2068057945314415</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2564132523547962</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.215865058460059</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1402896558345736</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1107328447017578</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1256920966110085</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>23695</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18251</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41946</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.09881604665268408</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.07286535090738255</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.09923392647817926</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>16690; 32370</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12010; 25677</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>33116; 52794</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.191646982035466</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1557876395819013</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1581981066365815</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1375691519454732</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1358044245993105</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.136740316576032</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>96010</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>83936</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179946</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1164182585190881</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1151703064047047</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1211023747830282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>81248; 112983</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>71183; 99093</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>159367; 204211</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1618900306941603</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1603264590042789</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1551790388306557</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>15525</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>14701</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>30226</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>9320</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10156</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>21877</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24319</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>21057</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>40256</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>30633</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>21133</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>51766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>21886</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>14536</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>40910</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>41974</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29237</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>65923</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>26157</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>29852</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>56009</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>18331</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>22074</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>44443</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>34814</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>39101</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>69256</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>23695</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>18251</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>41946</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>16690</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>12010</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>33116</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>32370</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>25677</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>52794</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>96010</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>83936</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>179946</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>81248</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>71183</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>159367</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>112983</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>99093</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>204211</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>